--- a/01_analyses_states/West Bengal/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/West Bengal/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6.5</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +415,13 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>22.6</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>100</v>
       </c>
       <c r="E4">
-        <v>61.3</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="5">
@@ -459,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="6">
@@ -472,13 +472,13 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3.2</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C7">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="C8">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C2">
-        <v>55.3</v>
+        <v>56.3</v>
       </c>
       <c r="D2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2">
-        <v>72.2</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3">
-        <v>44.7</v>
+        <v>43.7</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>27.8</v>
+        <v>26.6</v>
       </c>
     </row>
   </sheetData>

--- a/01_analyses_states/West Bengal/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/West Bengal/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11.9</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +415,13 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>23.8</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>100</v>
       </c>
       <c r="E4">
-        <v>54.8</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="5">
@@ -459,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="6">
@@ -472,13 +472,13 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C7">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="C8">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C4">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/West Bengal/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/West Bengal/results/SoIB_summaries.xlsx
@@ -396,13 +396,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>7</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>18.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +412,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>15.8</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +425,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>20</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="E4">
-        <v>52.6</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -453,13 +444,10 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -474,11 +462,8 @@
       <c r="C6">
         <v>3</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
       <c r="E6">
-        <v>7.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +473,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C7">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="C8">
-        <v>507</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +618,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>693</v>
+        <v>685</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +675,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +688,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C4">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5">
@@ -772,7 +757,7 @@
         <v>58</v>
       </c>
       <c r="E2">
-        <v>73.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -788,10 +773,10 @@
         <v>43.7</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>26.6</v>
+        <v>30.1</v>
       </c>
     </row>
   </sheetData>
